--- a/instance/uploads/old_warehouse.xlsx
+++ b/instance/uploads/old_warehouse.xlsx
@@ -1,43 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EvGen\Desktop\QR\project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>49fcd20a</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>49fcd90a</t>
+  </si>
+  <si>
+    <t>Молоток</t>
+  </si>
+  <si>
+    <t>1-1-1</t>
+  </si>
+  <si>
+    <t>2-2-2</t>
+  </si>
+  <si>
+    <t>3-3-3</t>
+  </si>
+  <si>
+    <t>Принтер</t>
+  </si>
+  <si>
+    <t>Отвертка</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -46,81 +132,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,14 +447,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="2"/>
+      <c r="C5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="2"/>
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="C7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+      <c r="C21"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+      <c r="C22"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+      <c r="C24"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>